--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:12:46+00:00</t>
+    <t>2026-02-10T10:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:23:53+00:00</t>
+    <t>2026-02-11T15:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:25:25+00:00</t>
+    <t>2026-02-16T10:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:19:26+00:00</t>
+    <t>2026-02-23T14:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T14:19:51+00:00</t>
+    <t>2026-02-24T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/CodeSystem-tddui-task-output-bilan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:04:30+00:00</t>
+    <t>2026-02-26T15:31:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
